--- a/data/trans_camb/IP21-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,47</t>
+          <t>-13,19; -1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 1,74</t>
+          <t>-10,48; 1,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -0,13</t>
+          <t>-12,17; -0,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 8,22</t>
+          <t>-5,71; 8,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 9,34</t>
+          <t>-5,62; 9,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 2,02</t>
+          <t>-10,06; 1,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 2,42</t>
+          <t>-7,04; 2,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 4,02</t>
+          <t>-5,55; 4,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,02; -0,38</t>
+          <t>-8,34; -0,27</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 48,13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 169,4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 107,58</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-72,47; 382,66</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-71,98; 344,34</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 93,53</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 53,2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-76,78; 392,56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-67,75; 409,87</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 281,22</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,81; 78,1</t>
+          <t>-82,43; 86,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,52; 120,83</t>
+          <t>-69,32; 127,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,51; 30,09</t>
+          <t>-91,97; 27,05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,84</t>
+          <t>-4,92; 4,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,68</t>
+          <t>-6,4; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 0,58</t>
+          <t>-7,3; 0,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 5,17</t>
+          <t>-4,22; 5,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 1,86</t>
+          <t>-6,06; 2,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 0,07</t>
+          <t>-6,92; 0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 3,54</t>
+          <t>-3,06; 3,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,68</t>
+          <t>-4,93; 0,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -0,63</t>
+          <t>-5,88; -0,63</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,62; 156,05</t>
+          <t>-69,61; 185,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-88,28; 79,76</t>
+          <t>-84,42; 88,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-99,06; 67,51</t>
+          <t>-100,0; 44,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,83; 200,77</t>
+          <t>-58,28; 230,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,81; 105,61</t>
+          <t>-86,47; 99,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,52</t>
+          <t>-93,63; 36,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 106,11</t>
+          <t>-48,3; 104,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,55; 24,84</t>
+          <t>-75,32; 35,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-88,18; -6,77</t>
+          <t>-89,32; -5,09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 3,43</t>
+          <t>-9,22; 3,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 0,8</t>
+          <t>-10,51; 0,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 2,79</t>
+          <t>-9,26; 2,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 6,39</t>
+          <t>-6,48; 6,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,61</t>
+          <t>-8,76; 2,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -0,44</t>
+          <t>-10,77; -0,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,46</t>
+          <t>-5,52; 3,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -0,29</t>
+          <t>-7,88; 0,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; -0,2</t>
+          <t>-7,89; -0,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,34; 140,16</t>
+          <t>-90,17; 152,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,26</t>
+          <t>-100,0; 87,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,84</t>
+          <t>-100,0; 146,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-72,09; 220,38</t>
+          <t>-71,2; 230,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,78</t>
+          <t>-90,2; 124,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,08</t>
+          <t>-100,0; 56,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-67,27; 85,18</t>
+          <t>-66,59; 96,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 3,31</t>
+          <t>-88,29; 20,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-88,68; 15,2</t>
+          <t>-89,56; 16,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 2,83</t>
+          <t>-4,66; 3,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 5,4</t>
+          <t>-3,8; 4,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 0,69</t>
+          <t>-6,14; 0,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 5,73</t>
+          <t>-6,22; 6,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 2,66</t>
+          <t>-8,79; 1,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,74; -1,07</t>
+          <t>-10,79; -1,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,66</t>
+          <t>-4,05; 3,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,23</t>
+          <t>-5,08; 2,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -1,12</t>
+          <t>-7,06; -1,26</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,85; 500,84</t>
+          <t>-83,13; 466,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,61; 273,96</t>
+          <t>-79,39; 265,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 202,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -8,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 153,77</t>
+          <t>-71,89; 154,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,31; 107,21</t>
+          <t>-79,43; 87,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,89</t>
+          <t>-100,0; -14,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 6,45</t>
+          <t>-9,91; 6,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -1,67</t>
+          <t>-16,11; -1,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -1,5</t>
+          <t>-14,76; -1,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,44</t>
+          <t>-1,52; 11,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,0</t>
+          <t>-7,83; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,0</t>
+          <t>-7,52; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 6,33</t>
+          <t>-3,51; 6,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,52; -1,44</t>
+          <t>-8,21; -1,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -1,44</t>
+          <t>-8,44; -1,49</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 364,24</t>
+          <t>-100,0; 437,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 409,22</t>
+          <t>-64,4; 393,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 13,08</t>
+          <t>0,02; 12,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 5,41</t>
+          <t>-3,72; 5,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 7,33</t>
+          <t>-3,34; 7,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 3,24</t>
+          <t>-8,25; 2,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 4,12</t>
+          <t>-7,66; 3,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 1,47</t>
+          <t>-8,78; 1,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,36</t>
+          <t>-2,94; 5,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 3,04</t>
+          <t>-4,62; 3,06</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,9</t>
+          <t>-4,4; 2,61</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-63,9; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 378,78</t>
+          <t>-62,57; 382,11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-84,03; 282,19</t>
+          <t>-87,06; 224,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,33; 247,81</t>
+          <t>-84,99; 210,79</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 8,14</t>
+          <t>0,24; 8,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 6,78</t>
+          <t>-0,87; 6,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,17</t>
+          <t>-4,1; 1,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,68</t>
+          <t>-5,99; 1,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 0,09</t>
+          <t>-7,22; 0,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 1,73</t>
+          <t>-6,44; 1,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,66</t>
+          <t>-1,99; 3,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,4</t>
+          <t>-2,94; 2,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,07</t>
+          <t>-3,97; 1,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 808,24</t>
+          <t>-16,77; 815,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 790,86</t>
+          <t>-38,14; 576,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 163,28</t>
+          <t>-100,0; 278,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-79,06; 59,19</t>
+          <t>-78,14; 66,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-88,64; 26,48</t>
+          <t>-91,4; 11,64</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-84,38; 78,9</t>
+          <t>-85,14; 80,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 134,75</t>
+          <t>-38,37; 138,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 92,23</t>
+          <t>-56,36; 88,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 54,84</t>
+          <t>-77,33; 56,14</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,93</t>
+          <t>-2,33; 2,94</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,04</t>
+          <t>-2,4; 2,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,77</t>
+          <t>-4,73; -0,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,69</t>
+          <t>-3,47; 2,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,79</t>
+          <t>-4,26; 1,78</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,28</t>
+          <t>-5,52; -0,32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,0</t>
+          <t>-2,13; 1,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,64</t>
+          <t>-2,45; 1,51</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,05; -0,82</t>
+          <t>-4,05; -0,85</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-79,61; 324,29</t>
+          <t>-73,56; 393,6</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,94; 423,52</t>
+          <t>-82,38; 354,81</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-70,39; 208,05</t>
+          <t>-68,84; 183,96</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-79,74; 121,64</t>
+          <t>-80,81; 119,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,65</t>
+          <t>-100,0; 39,68</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-54,95; 115,62</t>
+          <t>-55,31; 119,68</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 104,72</t>
+          <t>-63,14; 94,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,82</t>
+          <t>-100,0; 18,4</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,96</t>
+          <t>-1,25; 1,83</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,88</t>
+          <t>-2,23; 0,84</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,88</t>
+          <t>-3,7; -1,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,54</t>
+          <t>-1,91; 1,52</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,14</t>
+          <t>-3,28; -0,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -1,33</t>
+          <t>-4,57; -1,6</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,27</t>
+          <t>-1,11; 1,21</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,24</t>
+          <t>-2,38; -0,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,7</t>
+          <t>-3,7; -1,71</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 65,78</t>
+          <t>-28,2; 61,66</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 30,64</t>
+          <t>-49,63; 29,61</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-80,35; -29,27</t>
+          <t>-81,08; -35,09</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 42,21</t>
+          <t>-35,07; 40,78</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-61,94; -2,67</t>
+          <t>-60,88; -4,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-80,75; -36,7</t>
+          <t>-80,48; -38,28</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 35,77</t>
+          <t>-23,71; 35,79</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-49,87; -5,46</t>
+          <t>-49,0; -3,91</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-76,48; -46,52</t>
+          <t>-77,64; -46,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -1,41</t>
+          <t>-13,13; -1,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 1,9</t>
+          <t>-10,99; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; -0,52</t>
+          <t>-12,68; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 8,69</t>
+          <t>-6,76; 8,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 9,29</t>
+          <t>-5,63; 8,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 1,14</t>
+          <t>-9,23; 2,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,59</t>
+          <t>-6,75; 2,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 4,22</t>
+          <t>-5,42; 4,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -0,27</t>
+          <t>-8,66; -0,37</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,4</t>
+          <t>-100,0; 165,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 382,66</t>
+          <t>-81,75; 287,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,98; 344,34</t>
+          <t>-74,35; 330,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,43; 86,89</t>
+          <t>-81,08; 85,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 127,0</t>
+          <t>-66,19; 141,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,97; 27,05</t>
+          <t>-93,26; 7,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,3</t>
+          <t>-5,06; 3,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 1,58</t>
+          <t>-6,35; 2,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,53</t>
+          <t>-8,48; 0,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 5,71</t>
+          <t>-4,27; 5,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 2,23</t>
+          <t>-6,66; 1,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,16</t>
+          <t>-6,97; 0,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,4</t>
+          <t>-3,1; 3,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,75</t>
+          <t>-5,3; 0,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; -0,63</t>
+          <t>-6,25; -0,63</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 185,19</t>
+          <t>-73,07; 159,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,42; 88,74</t>
+          <t>-83,95; 121,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 44,14</t>
+          <t>-100,0; 55,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 230,5</t>
+          <t>-60,04; 214,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 99,55</t>
+          <t>-88,78; 102,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-93,63; 36,79</t>
+          <t>-94,13; 48,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 104,2</t>
+          <t>-46,7; 103,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 35,67</t>
+          <t>-78,8; 34,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,32; -5,09</t>
+          <t>-90,73; -9,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 3,7</t>
+          <t>-8,97; 3,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 0,55</t>
+          <t>-11,65; -0,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 2,57</t>
+          <t>-10,04; 2,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 6,07</t>
+          <t>-6,75; 6,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 2,4</t>
+          <t>-9,05; 2,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -0,27</t>
+          <t>-10,75; -0,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,62</t>
+          <t>-5,69; 3,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 0,21</t>
+          <t>-8,01; -0,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -0,02</t>
+          <t>-8,05; -0,07</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,17; 152,09</t>
+          <t>-87,63; 144,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,4</t>
+          <t>-100,0; 70,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,62</t>
+          <t>-100,0; 120,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 230,07</t>
+          <t>-73,38; 221,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,2; 124,21</t>
+          <t>-100,0; 120,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,66</t>
+          <t>-100,0; 48,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,59; 96,24</t>
+          <t>-65,49; 86,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,29; 20,05</t>
+          <t>-88,22; 3,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,56; 16,93</t>
+          <t>-89,75; 7,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 3,1</t>
+          <t>-5,43; 2,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,93</t>
+          <t>-3,9; 5,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 0,67</t>
+          <t>-6,2; 0,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 6,46</t>
+          <t>-6,61; 6,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 1,86</t>
+          <t>-7,48; 2,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -1,3</t>
+          <t>-9,96; -0,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,34</t>
+          <t>-3,7; 3,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 2,04</t>
+          <t>-4,69; 2,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -1,26</t>
+          <t>-6,75; -1,07</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 466,64</t>
+          <t>-81,64; 629,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-79,39; 265,52</t>
+          <t>-82,07; 300,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,91; 225,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,79</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-71,89; 154,34</t>
+          <t>-64,84; 168,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,43; 87,58</t>
+          <t>-76,43; 116,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,67</t>
+          <t>-100,0; -2,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 6,3</t>
+          <t>-9,71; 6,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,11; -1,7</t>
+          <t>-15,31; -1,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,76; -1,69</t>
+          <t>-14,11; -1,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 11,77</t>
+          <t>-1,55; 11,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,0</t>
+          <t>-7,5; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 0,0</t>
+          <t>-7,46; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 6,86</t>
+          <t>-3,02; 7,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,21; -1,49</t>
+          <t>-9,19; -1,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -1,49</t>
+          <t>-8,45; -1,48</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 437,97</t>
+          <t>-100,0; 486,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 393,15</t>
+          <t>-59,11; 597,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,02; 12,92</t>
+          <t>-0,71; 12,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,28</t>
+          <t>-3,68; 5,51</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 7,13</t>
+          <t>-3,64; 6,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 2,72</t>
+          <t>-7,87; 2,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 3,32</t>
+          <t>-7,1; 3,57</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 1,39</t>
+          <t>-8,11; 1,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,87</t>
+          <t>-2,68; 5,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 3,06</t>
+          <t>-4,38; 3,13</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,61</t>
+          <t>-4,75; 2,4</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,9; —</t>
+          <t>-50,04; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 382,11</t>
+          <t>-58,67; 382,14</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 224,31</t>
+          <t>-83,1; 240,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-84,99; 210,79</t>
+          <t>-87,86; 160,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,46</t>
+          <t>-0,1; 8,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 6,5</t>
+          <t>-1,05; 6,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1,31</t>
+          <t>-4,2; 1,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,82</t>
+          <t>-5,86; 1,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,01</t>
+          <t>-7,24; 0,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 1,69</t>
+          <t>-5,99; 2,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,8</t>
+          <t>-2,08; 3,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,22</t>
+          <t>-3,05; 2,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,11</t>
+          <t>-4,22; 0,99</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 815,42</t>
+          <t>-20,94; 755,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-38,14; 576,0</t>
+          <t>-39,49; 686,69</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 278,69</t>
+          <t>-100,0; 227,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-78,14; 66,01</t>
+          <t>-74,8; 84,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-91,4; 11,64</t>
+          <t>-89,18; 41,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-85,14; 80,99</t>
+          <t>-82,32; 105,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 138,67</t>
+          <t>-43,0; 144,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 88,17</t>
+          <t>-56,65; 86,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 56,14</t>
+          <t>-76,28; 61,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,94</t>
+          <t>-2,16; 3,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,7</t>
+          <t>-2,13; 3,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -0,7</t>
+          <t>-4,44; -0,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,9</t>
+          <t>-3,52; 2,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,78</t>
+          <t>-3,98; 1,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,52; -0,32</t>
+          <t>-5,5; -0,34</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,94</t>
+          <t>-1,83; 2,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,51</t>
+          <t>-2,27; 1,56</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,05; -0,85</t>
+          <t>-4,03; -0,82</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-73,56; 393,6</t>
+          <t>-72,38; 426,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 354,81</t>
+          <t>-71,27; 351,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2310,32 +2310,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 183,96</t>
+          <t>-70,45; 170,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-80,81; 119,41</t>
+          <t>-77,78; 157,69</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 119,68</t>
+          <t>-49,81; 135,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,14; 94,76</t>
+          <t>-62,03; 88,32</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,4</t>
+          <t>-100,0; -31,07</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,83</t>
+          <t>-1,43; 1,95</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,84</t>
+          <t>-2,18; 0,8</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,07</t>
+          <t>-3,79; -1,04</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,52</t>
+          <t>-1,94; 1,64</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,2</t>
+          <t>-3,37; -0,13</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -1,6</t>
+          <t>-4,47; -1,39</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,21</t>
+          <t>-1,22; 1,28</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,17</t>
+          <t>-2,34; -0,14</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,71</t>
+          <t>-3,71; -1,72</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 61,66</t>
+          <t>-30,8; 66,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 29,61</t>
+          <t>-49,13; 25,8</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-81,08; -35,09</t>
+          <t>-79,88; -31,95</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 40,78</t>
+          <t>-35,0; 45,41</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-60,88; -4,17</t>
+          <t>-61,92; -3,66</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-80,48; -38,28</t>
+          <t>-79,56; -32,97</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 35,79</t>
+          <t>-25,63; 35,94</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -3,91</t>
+          <t>-49,36; -4,05</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-77,64; -46,27</t>
+          <t>-76,34; -46,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-3,26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-5,73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,93</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,38</t>
+          <t>-4,65</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,11</t>
+          <t>-3,91</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -1,11</t>
+          <t>-6,24; 8,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 2,01</t>
+          <t>-5,11; 9,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 0,0</t>
+          <t>-9,1; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 8,08</t>
+          <t>-11,82; -1,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 8,94</t>
+          <t>-9,96; 1,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 2,0</t>
+          <t>-10,89; 0,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 2,5</t>
+          <t>-6,94; 2,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,76</t>
+          <t>-4,99; 4,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -0,37</t>
+          <t>-7,59; 0,07</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-58,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-87,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-54,92%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-75,06%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-60,69%</t>
+          <t>-70,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-68,11%</t>
+          <t>-64,8%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-76,78; 392,56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-67,75; 409,87</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 301,74</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 165,01</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-81,75; 287,91</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,35; 330,92</t>
+          <t>-100,0; 93,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 76,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,08; 85,9</t>
+          <t>-80,81; 78,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,19; 141,29</t>
+          <t>-61,52; 120,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-93,26; 7,13</t>
+          <t>-90,95; 35,1</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,12</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,29</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-2,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,96</t>
+          <t>-3,74; 5,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 2,17</t>
+          <t>-6,6; 1,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,29</t>
+          <t>-7,58; -0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 5,65</t>
+          <t>-5,28; 3,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 1,89</t>
+          <t>-6,84; 1,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,08</t>
+          <t>-7,0; 1,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 3,5</t>
+          <t>-3,23; 3,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,86</t>
+          <t>-5,0; 0,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,63</t>
+          <t>-5,81; -0,29</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-43,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-68,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-11,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-40,51%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-64,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-43,88%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-66,12%</t>
+          <t>-53,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-65,38%</t>
+          <t>-61,4%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,07; 159,53</t>
+          <t>-57,83; 200,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,95; 121,21</t>
+          <t>-88,81; 105,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,74</t>
+          <t>-96,21; 67,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 214,72</t>
+          <t>-73,62; 156,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,78; 102,11</t>
+          <t>-88,28; 79,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-94,13; 48,39</t>
+          <t>-90,94; 133,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 103,05</t>
+          <t>-50,46; 106,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,8; 34,36</t>
+          <t>-75,55; 24,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-90,73; -9,1</t>
+          <t>-85,95; 9,47</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,28</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,71</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,22</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,9</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,28</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,61</t>
+          <t>-2,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-3,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,49</t>
+          <t>-6,61; 6,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; -0,07</t>
+          <t>-8,54; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 2,47</t>
+          <t>-10,82; -0,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 6,06</t>
+          <t>-8,53; 3,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 2,15</t>
+          <t>-10,64; 0,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -0,18</t>
+          <t>-9,13; 2,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 3,15</t>
+          <t>-5,37; 3,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -0,22</t>
+          <t>-7,78; -0,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,05; -0,07</t>
+          <t>-7,89; -0,13</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,69%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-52,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-75,44%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-35,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-68,17%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-46,86%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,69%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-52,47%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-73,8%</t>
+          <t>-45,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-61,33%</t>
+          <t>-60,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 144,25</t>
+          <t>-72,09; 220,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,3</t>
+          <t>-100,0; 226,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,95</t>
+          <t>-100,0; 20,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 221,77</t>
+          <t>-89,34; 140,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,82</t>
+          <t>-100,0; 93,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,55</t>
+          <t>-100,0; 235,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 86,16</t>
+          <t>-67,27; 85,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,22; 3,94</t>
+          <t>-89,73; 3,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,75; 7,96</t>
+          <t>-88,86; 17,08</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,68</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,63</t>
+          <t>-2,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,96</t>
+          <t>-6,54; 5,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,02</t>
+          <t>-7,96; 2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,76</t>
+          <t>-10,77; -1,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 6,42</t>
+          <t>-4,98; 2,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 2,64</t>
+          <t>-3,74; 5,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -0,89</t>
+          <t>-6,73; 0,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,61</t>
+          <t>-3,85; 3,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,76</t>
+          <t>-4,78; 2,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -1,07</t>
+          <t>-6,63; -1,2</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-1,13%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-50,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-88,17%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-26,59%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>15,17%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-74,87%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,13%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-50,24%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-87,22%</t>
+          <t>-76,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-82,88%</t>
+          <t>-83,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>-84,61; 273,96</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 202,14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-81,64; 629,05</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-82,07; 300,34</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-90,91; 225,0</t>
+          <t>-84,85; 500,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,84; 168,91</t>
+          <t>-66,66; 153,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,43; 116,63</t>
+          <t>-77,31; 107,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,84</t>
+          <t>-100,0; -25,73</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,34</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,5</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,53</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-6,38</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-6,38</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,34</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 6,66</t>
+          <t>-1,49; 10,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -1,66</t>
+          <t>-7,55; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -1,66</t>
+          <t>-6,57; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 11,84</t>
+          <t>-9,55; 6,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,0</t>
+          <t>-15,55; -1,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 0,0</t>
+          <t>-14,39; -1,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 7,6</t>
+          <t>-3,94; 6,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -1,49</t>
+          <t>-8,52; -1,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,45; -1,48</t>
+          <t>-8,34; -1,44</t>
         </is>
       </c>
     </row>
@@ -1594,22 +1594,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>289,5%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-23,97%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>289,5%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 486,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1662,22 +1662,22 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 364,24</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 597,57</t>
+          <t>-67,39; 409,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,59</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,85</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>5,3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,26</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-2,59</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 12,88</t>
+          <t>-7,77; 3,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,51</t>
+          <t>-7,56; 4,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,77</t>
+          <t>-8,55; 1,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 2,97</t>
+          <t>-0,89; 13,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,57</t>
+          <t>-4,55; 5,41</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,76</t>
+          <t>-3,68; 6,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,84</t>
+          <t>-2,86; 5,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 3,13</t>
+          <t>-4,23; 3,04</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,4</t>
+          <t>-4,62; 2,3</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-59,01%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-38,54%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-65,0%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>223,32%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>10,93%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>55,94%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-59,01%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-38,54%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-59,72%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-22,67%</t>
+          <t>-31,49%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,04; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-58,67; 382,14</t>
+          <t>-60,0; 378,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-83,1; 240,2</t>
+          <t>-84,03; 282,19</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-87,86; 160,13</t>
+          <t>-84,28; 212,28</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,76</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-3,14</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2,68</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,56</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 8,19</t>
+          <t>-6,47; 1,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 6,73</t>
+          <t>-7,11; 0,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,08</t>
+          <t>-6,05; 2,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,84</t>
+          <t>-0,2; 8,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 0,4</t>
+          <t>-0,82; 6,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 2,2</t>
+          <t>-4,16; 1,14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,87</t>
+          <t>-2,17; 3,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,08</t>
+          <t>-3,11; 2,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,99</t>
+          <t>-4,23; 1,33</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-33,09%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-59,11%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-36,59%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>148,55%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>104,64%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-47,42%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-33,09%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-59,11%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-41,83%</t>
+          <t>-49,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-41,7%</t>
+          <t>-39,34%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 755,28</t>
+          <t>-79,06; 59,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 686,69</t>
+          <t>-88,64; 26,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,24</t>
+          <t>-83,16; 105,14</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-74,8; 84,23</t>
+          <t>-29,06; 808,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-89,18; 41,73</t>
+          <t>-36,53; 790,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-82,32; 105,18</t>
+          <t>-100,0; 157,05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-43,0; 144,42</t>
+          <t>-42,94; 134,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-56,65; 86,22</t>
+          <t>-55,84; 92,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-76,28; 61,65</t>
+          <t>-75,7; 68,36</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,99</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-2,59</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,37</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-2,06</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-2,57</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>0,07</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,07</t>
+          <t>-3,29; 2,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,02</t>
+          <t>-3,98; 1,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,44; -0,77</t>
+          <t>-5,31; -0,24</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,64</t>
+          <t>-2,18; 2,93</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,87</t>
+          <t>-2,21; 3,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,5; -0,34</t>
+          <t>-4,5; -0,77</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,19</t>
+          <t>-2,03; 2,0</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,56</t>
+          <t>-2,3; 1,64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,82</t>
+          <t>-4,06; -0,79</t>
         </is>
       </c>
     </row>
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-6,74%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-29,7%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-77,53%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>18,02%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>15,43%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-6,74%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-29,7%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-77,01%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-84,6%</t>
+          <t>-85,28%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 426,78</t>
+          <t>-70,39; 208,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-71,27; 351,3</t>
+          <t>-79,74; 121,64</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 96,04</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>-79,61; 324,29</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>-72,94; 423,52</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>-70,45; 170,83</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>-77,78; 157,69</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 135,39</t>
+          <t>-54,95; 115,62</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 88,32</t>
+          <t>-63,75; 104,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,07</t>
+          <t>-100,0; -14,52</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-2,97</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-2,66</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,95</t>
+          <t>-1,92; 1,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,8</t>
+          <t>-3,52; -0,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -1,04</t>
+          <t>-4,53; -1,37</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,64</t>
+          <t>-1,41; 1,96</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,13</t>
+          <t>-2,23; 0,88</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,47; -1,39</t>
+          <t>-3,69; -0,9</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,28</t>
+          <t>-1,34; 1,27</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,14</t>
+          <t>-2,42; -0,24</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,71; -1,72</t>
+          <t>-3,7; -1,69</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-3,43%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-39,43%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-64,78%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-19,09%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-62,86%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-3,43%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-39,43%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-64,35%</t>
+          <t>-62,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-63,59%</t>
+          <t>-63,65%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 66,89</t>
+          <t>-34,68; 42,21</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 25,8</t>
+          <t>-61,94; -2,67</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-79,88; -31,95</t>
+          <t>-80,71; -36,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 45,41</t>
+          <t>-31,31; 65,78</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -3,66</t>
+          <t>-48,44; 30,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-79,56; -32,97</t>
+          <t>-80,36; -29,87</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 35,94</t>
+          <t>-28,09; 35,77</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -4,05</t>
+          <t>-49,87; -5,46</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-76,34; -46,09</t>
+          <t>-76,49; -46,32</t>
         </is>
       </c>
     </row>
